--- a/workshop_registration_form_templates/026_nonprofit_tech_skills_training_registration_form--workshop_registration_form_templates.xlsx
+++ b/workshop_registration_form_templates/026_nonprofit_tech_skills_training_registration_form--workshop_registration_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>web_development</t>
+          <t>web development</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>data_sciences</t>
+          <t>data sciences</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>cloud_computing</t>
+          <t>cloud computing</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>database_administration</t>
+          <t>database administration</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>artificial_intelligence</t>
+          <t>artificial intelligence</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>data_analysis</t>
+          <t>data analysis</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>data_visualization</t>
+          <t>data visualization</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>data_sciences</t>
+          <t>data sciences</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>web_development</t>
+          <t>web development</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>web_development</t>
+          <t>web development</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>database_administration</t>
+          <t>database administration</t>
         </is>
       </c>
     </row>
